--- a/tests/TC-06/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-06/results/timetable_all_departments_even.xlsx
@@ -78,8 +78,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,8 +90,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-        <bgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
@@ -204,10 +204,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -817,9 +817,9 @@
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>CS601
+          <t>CS602
 LEC
-Room: 101
+Room: 102
 TBD</t>
         </is>
       </c>
@@ -838,16 +838,9 @@
       <c r="N2" s="8" t="inlineStr"/>
       <c r="O2" s="8" t="inlineStr"/>
       <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="13" t="inlineStr">
-        <is>
-          <t>CS602
-LEC
-Room: 102
-TBD</t>
-        </is>
-      </c>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="11" t="n"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
@@ -869,17 +862,10 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr"/>
       <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>CS602
-LEC
-Room: 102
-TBD</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="11" t="n"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
       <c r="L3" s="12" t="inlineStr">
@@ -913,10 +899,17 @@
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>CS602
+LEC
+Room: 102
+TBD</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="11" t="n"/>
       <c r="H4" s="8" t="inlineStr"/>
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
@@ -929,38 +922,7 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
       <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="13" t="inlineStr">
-        <is>
-          <t>CS602
-TUT
-Room: 102
-TBD</t>
-        </is>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t>CS601
 LEC
@@ -968,9 +930,33 @@
 TBD</t>
         </is>
       </c>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="10" t="n"/>
-      <c r="H5" s="11" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="11" t="n"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
@@ -984,8 +970,15 @@
       <c r="O5" s="8" t="inlineStr"/>
       <c r="P5" s="8" t="inlineStr"/>
       <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>CS602
+TUT
+Room: 101
+TBD</t>
+        </is>
+      </c>
+      <c r="S5" s="11" t="n"/>
       <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
@@ -1005,8 +998,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>CS603
 LEC
@@ -1014,19 +1006,27 @@
 TBD</t>
         </is>
       </c>
+      <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
-      <c r="J6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>CS601
+LEC
+Room: 101
+TBD</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="n"/>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
@@ -1163,12 +1163,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="P4:R4"/>
     <mergeCell ref="E2:H2"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1329,9 +1330,9 @@
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>CS601
+          <t>CS602
 LEC
-Room: 101
+Room: 102
 TBD</t>
         </is>
       </c>
@@ -1350,16 +1351,9 @@
       <c r="N2" s="8" t="inlineStr"/>
       <c r="O2" s="8" t="inlineStr"/>
       <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="13" t="inlineStr">
-        <is>
-          <t>CS602
-LEC
-Room: 102
-TBD</t>
-        </is>
-      </c>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="11" t="n"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
@@ -1381,17 +1375,10 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr"/>
       <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>CS602
-LEC
-Room: 102
-TBD</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="11" t="n"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
       <c r="L3" s="12" t="inlineStr">
@@ -1425,10 +1412,17 @@
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>CS602
+LEC
+Room: 102
+TBD</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="11" t="n"/>
       <c r="H4" s="8" t="inlineStr"/>
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
@@ -1441,38 +1435,7 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
       <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="13" t="inlineStr">
-        <is>
-          <t>CS602
-TUT
-Room: 102
-TBD</t>
-        </is>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t>CS601
 LEC
@@ -1480,9 +1443,33 @@
 TBD</t>
         </is>
       </c>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="10" t="n"/>
-      <c r="H5" s="11" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="11" t="n"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
@@ -1496,8 +1483,15 @@
       <c r="O5" s="8" t="inlineStr"/>
       <c r="P5" s="8" t="inlineStr"/>
       <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>CS602
+TUT
+Room: 101
+TBD</t>
+        </is>
+      </c>
+      <c r="S5" s="11" t="n"/>
       <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
@@ -1517,8 +1511,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>CS603
 LEC
@@ -1526,19 +1519,27 @@
 TBD</t>
         </is>
       </c>
+      <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
-      <c r="J6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>CS601
+LEC
+Room: 101
+TBD</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="n"/>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
@@ -1675,12 +1676,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="P4:R4"/>
     <mergeCell ref="E2:H2"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1692,7 +1694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1759,7 +1761,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1769,7 +1771,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS601</t>
+          <t>CS602</t>
         </is>
       </c>
     </row>
@@ -1780,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1816,13 +1818,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1831,7 +1833,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1841,7 +1843,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CS602</t>
+          <t>CS601</t>
         </is>
       </c>
     </row>
@@ -1855,10 +1857,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1872,12 +1874,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CS601</t>
+          <t>CS602</t>
         </is>
       </c>
     </row>
@@ -1891,10 +1893,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1920,17 +1922,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1963,10 +1965,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1996,13 +1998,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2032,13 +2034,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2068,32 +2070,104 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CS602</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>6</v>
       </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>LEC</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>CS603</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CS601</t>
         </is>
       </c>
     </row>

--- a/tests/TC-06/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-06/results/timetable_all_departments_even.xlsx
@@ -143,14 +143,14 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -182,18 +182,18 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -813,35 +813,35 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>CS602
 LEC
-Room: 102
-TBD</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+Room: 101
+TBD_CS602</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr"/>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="10" t="inlineStr"/>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="8" t="inlineStr"/>
-      <c r="S2" s="8" t="inlineStr"/>
-      <c r="T2" s="8" t="inlineStr"/>
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
+      <c r="O2" s="10" t="inlineStr"/>
+      <c r="P2" s="10" t="inlineStr"/>
+      <c r="Q2" s="10" t="inlineStr"/>
+      <c r="R2" s="10" t="inlineStr"/>
+      <c r="S2" s="10" t="inlineStr"/>
+      <c r="T2" s="10" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -859,28 +859,42 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>CS601
+LEC
+Room: 102
+TBD_CS601</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="10" t="inlineStr"/>
+      <c r="G3" s="10" t="inlineStr"/>
+      <c r="H3" s="10" t="inlineStr"/>
+      <c r="I3" s="10" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr"/>
+      <c r="K3" s="10" t="inlineStr"/>
+      <c r="L3" s="11" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr"/>
+      <c r="M3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
+      <c r="O3" s="10" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr">
+        <is>
+          <t>CS602
+LEC
+Room: 101
+TBD_CS602</t>
+        </is>
+      </c>
+      <c r="Q3" s="13" t="n"/>
+      <c r="R3" s="9" t="n"/>
+      <c r="S3" s="10" t="inlineStr"/>
+      <c r="T3" s="10" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -898,42 +912,42 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>CS602
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>CS603
+LEC
+Room: 101
+TBD_CS603</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="10" t="inlineStr"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr"/>
+      <c r="K4" s="10" t="inlineStr"/>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
+      <c r="O4" s="10" t="inlineStr"/>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>CS601
 LEC
 Room: 102
-TBD</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="13" t="inlineStr">
-        <is>
-          <t>CS601
-LEC
-Room: 101
-TBD</t>
-        </is>
-      </c>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="11" t="n"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
+TBD_CS601</t>
+        </is>
+      </c>
+      <c r="Q4" s="13" t="n"/>
+      <c r="R4" s="9" t="n"/>
+      <c r="S4" s="10" t="inlineStr"/>
+      <c r="T4" s="10" t="inlineStr"/>
       <c r="U4" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -951,88 +965,74 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="10" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr"/>
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="9" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
+      <c r="O5" s="10" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr"/>
+      <c r="Q5" s="10" t="inlineStr"/>
+      <c r="R5" s="10" t="inlineStr"/>
+      <c r="S5" s="10" t="inlineStr"/>
+      <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
+      <c r="O6" s="10" t="inlineStr"/>
+      <c r="P6" s="10" t="inlineStr"/>
+      <c r="Q6" s="10" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr">
         <is>
           <t>CS602
 TUT
 Room: 101
-TBD</t>
-        </is>
-      </c>
-      <c r="S5" s="11" t="n"/>
-      <c r="T5" s="8" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>CS603
-LEC
-Room: 101
-TBD</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="13" t="inlineStr">
-        <is>
-          <t>CS601
-LEC
-Room: 101
-TBD</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
+TBD_CS602</t>
+        </is>
+      </c>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="10" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS601</t>
         </is>
       </c>
       <c r="E12" s="17" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS602</t>
         </is>
       </c>
       <c r="E13" s="17" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS603</t>
         </is>
       </c>
       <c r="E14" s="17" t="inlineStr">
@@ -1164,12 +1164,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="R6:S6"/>
     <mergeCell ref="P4:R4"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="P3:R3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1326,35 +1326,35 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>CS602
 LEC
-Room: 102
-TBD</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+Room: 101
+TBD_CS602</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr"/>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="10" t="inlineStr"/>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="8" t="inlineStr"/>
-      <c r="S2" s="8" t="inlineStr"/>
-      <c r="T2" s="8" t="inlineStr"/>
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
+      <c r="O2" s="10" t="inlineStr"/>
+      <c r="P2" s="10" t="inlineStr"/>
+      <c r="Q2" s="10" t="inlineStr"/>
+      <c r="R2" s="10" t="inlineStr"/>
+      <c r="S2" s="10" t="inlineStr"/>
+      <c r="T2" s="10" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1372,28 +1372,42 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>CS601
+LEC
+Room: 102
+TBD_CS601</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="10" t="inlineStr"/>
+      <c r="G3" s="10" t="inlineStr"/>
+      <c r="H3" s="10" t="inlineStr"/>
+      <c r="I3" s="10" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr"/>
+      <c r="K3" s="10" t="inlineStr"/>
+      <c r="L3" s="11" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr"/>
+      <c r="M3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
+      <c r="O3" s="10" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr">
+        <is>
+          <t>CS602
+LEC
+Room: 101
+TBD_CS602</t>
+        </is>
+      </c>
+      <c r="Q3" s="13" t="n"/>
+      <c r="R3" s="9" t="n"/>
+      <c r="S3" s="10" t="inlineStr"/>
+      <c r="T3" s="10" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1411,42 +1425,42 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>CS602
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>CS603
+LEC
+Room: 101
+TBD_CS603</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="10" t="inlineStr"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr"/>
+      <c r="K4" s="10" t="inlineStr"/>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
+      <c r="O4" s="10" t="inlineStr"/>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>CS601
 LEC
 Room: 102
-TBD</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="13" t="inlineStr">
-        <is>
-          <t>CS601
-LEC
-Room: 101
-TBD</t>
-        </is>
-      </c>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="11" t="n"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
+TBD_CS601</t>
+        </is>
+      </c>
+      <c r="Q4" s="13" t="n"/>
+      <c r="R4" s="9" t="n"/>
+      <c r="S4" s="10" t="inlineStr"/>
+      <c r="T4" s="10" t="inlineStr"/>
       <c r="U4" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1464,88 +1478,74 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="10" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr"/>
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="9" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
+      <c r="O5" s="10" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr"/>
+      <c r="Q5" s="10" t="inlineStr"/>
+      <c r="R5" s="10" t="inlineStr"/>
+      <c r="S5" s="10" t="inlineStr"/>
+      <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
+      <c r="O6" s="10" t="inlineStr"/>
+      <c r="P6" s="10" t="inlineStr"/>
+      <c r="Q6" s="10" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr">
         <is>
           <t>CS602
 TUT
 Room: 101
-TBD</t>
-        </is>
-      </c>
-      <c r="S5" s="11" t="n"/>
-      <c r="T5" s="8" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>CS603
-LEC
-Room: 101
-TBD</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="13" t="inlineStr">
-        <is>
-          <t>CS601
-LEC
-Room: 101
-TBD</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
+TBD_CS602</t>
+        </is>
+      </c>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="10" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS601</t>
         </is>
       </c>
       <c r="E12" s="17" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS602</t>
         </is>
       </c>
       <c r="E13" s="17" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS603</t>
         </is>
       </c>
       <c r="E14" s="17" t="inlineStr">
@@ -1677,12 +1677,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="R6:S6"/>
     <mergeCell ref="P4:R4"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="P3:R3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1749,19 +1749,19 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS602</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1782,17 +1782,17 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="C3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>7</v>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS601</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CS602</t>
+          <t>CS601</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>16</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS602</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CS601</t>
+          <t>CS602</t>
         </is>
       </c>
     </row>
@@ -1854,17 +1854,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS603</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CS602</t>
+          <t>CS603</t>
         </is>
       </c>
     </row>
@@ -1890,22 +1890,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS601</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CS603</t>
+          <t>CS601</t>
         </is>
       </c>
     </row>
@@ -1929,14 +1929,14 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS602</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CS601</t>
+          <t>CS602</t>
         </is>
       </c>
     </row>
@@ -1965,19 +1965,19 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS602</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1998,17 +1998,17 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
         <v>4</v>
       </c>
-      <c r="C9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7</v>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS601</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CS602</t>
+          <t>CS601</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>16</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS602</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CS601</t>
+          <t>CS602</t>
         </is>
       </c>
     </row>
@@ -2070,17 +2070,17 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS603</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CS602</t>
+          <t>CS603</t>
         </is>
       </c>
     </row>
@@ -2106,22 +2106,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS601</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CS603</t>
+          <t>CS601</t>
         </is>
       </c>
     </row>
@@ -2145,14 +2145,14 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD_CS602</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CS601</t>
+          <t>CS602</t>
         </is>
       </c>
     </row>
